--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121164194</v>
+        <v>121164626</v>
       </c>
       <c r="B2" t="n">
-        <v>97025</v>
+        <v>97998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526878</v>
+        <v>526881</v>
       </c>
       <c r="R2" t="n">
-        <v>6770212</v>
+        <v>6770224</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164626</v>
+        <v>121164185</v>
       </c>
       <c r="B3" t="n">
-        <v>97988</v>
+        <v>97035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526881</v>
+        <v>526916</v>
       </c>
       <c r="R3" t="n">
-        <v>6770224</v>
+        <v>6770226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164185</v>
+        <v>121164194</v>
       </c>
       <c r="B4" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526916</v>
+        <v>526878</v>
       </c>
       <c r="R4" t="n">
-        <v>6770226</v>
+        <v>6770212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>121266746</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164185</v>
+        <v>121164194</v>
       </c>
       <c r="B3" t="n">
         <v>97035</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526916</v>
+        <v>526878</v>
       </c>
       <c r="R3" t="n">
-        <v>6770226</v>
+        <v>6770212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164194</v>
+        <v>121164185</v>
       </c>
       <c r="B4" t="n">
         <v>97035</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526878</v>
+        <v>526916</v>
       </c>
       <c r="R4" t="n">
-        <v>6770212</v>
+        <v>6770226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121164626</v>
       </c>
       <c r="B2" t="n">
-        <v>97998</v>
+        <v>98011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164194</v>
+        <v>121164185</v>
       </c>
       <c r="B3" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526878</v>
+        <v>526916</v>
       </c>
       <c r="R3" t="n">
-        <v>6770212</v>
+        <v>6770226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164185</v>
+        <v>121164194</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526916</v>
+        <v>526878</v>
       </c>
       <c r="R4" t="n">
-        <v>6770226</v>
+        <v>6770212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>121266746</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121164626</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121164185</v>
       </c>
       <c r="B3" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>121164194</v>
       </c>
       <c r="B4" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121164626</v>
+        <v>121164185</v>
       </c>
       <c r="B2" t="n">
-        <v>98012</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526881</v>
+        <v>526916</v>
       </c>
       <c r="R2" t="n">
-        <v>6770224</v>
+        <v>6770226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164185</v>
+        <v>121164194</v>
       </c>
       <c r="B3" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526916</v>
+        <v>526878</v>
       </c>
       <c r="R3" t="n">
-        <v>6770226</v>
+        <v>6770212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164194</v>
+        <v>121164626</v>
       </c>
       <c r="B4" t="n">
-        <v>97049</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526878</v>
+        <v>526881</v>
       </c>
       <c r="R4" t="n">
-        <v>6770212</v>
+        <v>6770224</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>121266746</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121164185</v>
+        <v>121164626</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526916</v>
+        <v>526881</v>
       </c>
       <c r="R2" t="n">
-        <v>6770226</v>
+        <v>6770224</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164194</v>
+        <v>121164185</v>
       </c>
       <c r="B3" t="n">
         <v>97052</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526878</v>
+        <v>526916</v>
       </c>
       <c r="R3" t="n">
-        <v>6770212</v>
+        <v>6770226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164626</v>
+        <v>121164194</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>97052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526881</v>
+        <v>526878</v>
       </c>
       <c r="R4" t="n">
-        <v>6770224</v>
+        <v>6770212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121164626</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164185</v>
+        <v>121164194</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526916</v>
+        <v>526878</v>
       </c>
       <c r="R3" t="n">
-        <v>6770226</v>
+        <v>6770212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164194</v>
+        <v>121164185</v>
       </c>
       <c r="B4" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526878</v>
+        <v>526916</v>
       </c>
       <c r="R4" t="n">
-        <v>6770212</v>
+        <v>6770226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>121266746</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 32354-2023 artfynd.xlsx
+++ b/artfynd/A 32354-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>121266746</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
